--- a/r4-ELGA-e-Medikation-Review_Architektur/ValueSet-DurchgefuehrteAbgabeTypVS.xlsx
+++ b/r4-ELGA-e-Medikation-Review_Architektur/ValueSet-DurchgefuehrteAbgabeTypVS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T12:41:29+00:00</t>
+    <t>2026-06-22T13:11:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -87,7 +87,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>ValueSet für zulässige Ausprägungen eines Typs einer durchgeführten Abgabe (MedicationDispense).</t>
+    <t>ValueSet für zulässige Ausprägungen eines Typs einer Durchgeführten Abgabe (MedicationDispense).</t>
   </si>
   <si>
     <t>Purpose</t>
